--- a/DXLibProject_Start/Data/CSV/ActionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84D28CF-8E44-47C1-B99F-E8295C7693FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEF9D2C-13AD-4D46-96FA-48577B14B8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6210" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/DXLibProject_Start/Data/CSV/ActionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEF9D2C-13AD-4D46-96FA-48577B14B8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C007C7BA-F65C-445F-9AE8-374D80BF251E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,19 +62,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>CollisionID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EffectParamID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>IntervalID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>comment</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>effectParamID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>collisionID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>intervalID</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -482,16 +482,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -516,7 +516,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
